--- a/data/trans_orig/IP05A07-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP05A07-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>68234</t>
+          <t>68627</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>87579</t>
+          <t>88116</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>74325</t>
+          <t>73756</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>93065</t>
+          <t>93330</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>148843</t>
+          <t>147567</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>175501</t>
+          <t>175532</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>60,09%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42079</t>
+          <t>41808</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59630</t>
+          <t>60482</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33584</t>
+          <t>33142</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52483</t>
+          <t>51458</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>78862</t>
+          <t>79524</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>103848</t>
+          <t>106063</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>36,31%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11737</t>
+          <t>11828</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24169</t>
+          <t>24478</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13805</t>
+          <t>14359</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27458</t>
+          <t>27698</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28551</t>
+          <t>28286</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>48570</t>
+          <t>47909</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>113084</t>
+          <t>113889</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>138098</t>
+          <t>138922</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>121901</t>
+          <t>121704</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>149208</t>
+          <t>147692</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>242992</t>
+          <t>241639</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>280503</t>
+          <t>278384</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>55,1%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>76701</t>
+          <t>75928</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>100779</t>
+          <t>100362</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>84034</t>
+          <t>85087</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>112416</t>
+          <t>111142</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>169389</t>
+          <t>168469</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>205439</t>
+          <t>205788</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,73%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14906</t>
+          <t>15438</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28817</t>
+          <t>30052</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28037</t>
+          <t>27598</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46438</t>
+          <t>46004</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47405</t>
+          <t>47081</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70727</t>
+          <t>71506</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,15%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>78534</t>
+          <t>79138</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>99047</t>
+          <t>99457</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>67366</t>
+          <t>68103</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>88397</t>
+          <t>89108</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>152944</t>
+          <t>150031</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>181214</t>
+          <t>181941</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,65%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38448</t>
+          <t>38141</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57852</t>
+          <t>57126</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50438</t>
+          <t>49393</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71641</t>
+          <t>69900</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>94054</t>
+          <t>93320</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>120893</t>
+          <t>123502</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>39,13%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14703</t>
+          <t>14547</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28581</t>
+          <t>28277</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14662</t>
+          <t>14946</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28270</t>
+          <t>28718</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32345</t>
+          <t>31311</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51803</t>
+          <t>51827</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>77504</t>
+          <t>77831</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>98895</t>
+          <t>99280</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>89148</t>
+          <t>88701</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>109902</t>
+          <t>110296</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>172724</t>
+          <t>172373</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>203277</t>
+          <t>201355</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>57,44%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46668</t>
+          <t>47078</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>66547</t>
+          <t>66776</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>51850</t>
+          <t>51666</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>71277</t>
+          <t>72198</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>103347</t>
+          <t>102367</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>131652</t>
+          <t>131649</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19149</t>
+          <t>18622</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35553</t>
+          <t>34642</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13415</t>
+          <t>13109</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26277</t>
+          <t>25885</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>35938</t>
+          <t>36217</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>57692</t>
+          <t>56208</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>358991</t>
+          <t>359659</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>402388</t>
+          <t>402182</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>374653</t>
+          <t>373723</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>421053</t>
+          <t>418506</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>747571</t>
+          <t>745526</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>811049</t>
+          <t>809093</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,28%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>223365</t>
+          <t>223314</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>264601</t>
+          <t>263770</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>238411</t>
+          <t>242236</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>283920</t>
+          <t>286961</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>473770</t>
+          <t>472162</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>533903</t>
+          <t>533286</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,44%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>72452</t>
+          <t>73045</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>101619</t>
+          <t>102445</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>80972</t>
+          <t>80006</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>110794</t>
+          <t>111102</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>161727</t>
+          <t>163777</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>200764</t>
+          <t>204858</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>14,0%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>80251</t>
+          <t>80313</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>96621</t>
+          <t>96918</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>80688</t>
+          <t>80277</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>96709</t>
+          <t>96685</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>163991</t>
+          <t>165465</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>187783</t>
+          <t>188440</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,82%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23614</t>
+          <t>23027</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38571</t>
+          <t>38187</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19956</t>
+          <t>20267</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34360</t>
+          <t>35136</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48638</t>
+          <t>47951</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69819</t>
+          <t>69179</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,1%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7485</t>
+          <t>7372</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17618</t>
+          <t>17417</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14162</t>
+          <t>12983</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13741</t>
+          <t>14326</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27628</t>
+          <t>28905</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>125879</t>
+          <t>126903</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>147430</t>
+          <t>148248</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>158982</t>
+          <t>158352</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>183470</t>
+          <t>183195</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>291244</t>
+          <t>292082</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>323768</t>
+          <t>325284</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,5%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46535</t>
+          <t>45860</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>66871</t>
+          <t>65965</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>51254</t>
+          <t>51945</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>73167</t>
+          <t>73864</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>103623</t>
+          <t>103783</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>133801</t>
+          <t>134257</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10756</t>
+          <t>10691</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23358</t>
+          <t>23357</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18116</t>
+          <t>17435</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33385</t>
+          <t>33194</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32175</t>
+          <t>32202</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52385</t>
+          <t>52046</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>112369</t>
+          <t>113887</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>135173</t>
+          <t>135120</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>112838</t>
+          <t>111407</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>133282</t>
+          <t>133211</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>230810</t>
+          <t>231891</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>262186</t>
+          <t>263037</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,81%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35377</t>
+          <t>35533</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56199</t>
+          <t>55242</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34412</t>
+          <t>33641</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53748</t>
+          <t>54009</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>76843</t>
+          <t>76392</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103358</t>
+          <t>103218</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,39%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13327</t>
+          <t>13169</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27573</t>
+          <t>27117</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14767</t>
+          <t>14425</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28997</t>
+          <t>29035</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31324</t>
+          <t>31573</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51623</t>
+          <t>51268</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,61%</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98812</t>
+          <t>97765</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>119219</t>
+          <t>119502</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>99617</t>
+          <t>100394</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>120833</t>
+          <t>120846</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>204572</t>
+          <t>204060</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>234778</t>
+          <t>231666</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>66,92%</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36915</t>
+          <t>36650</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>56822</t>
+          <t>57520</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31217</t>
+          <t>32260</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>50579</t>
+          <t>51009</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>73079</t>
+          <t>74966</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>99960</t>
+          <t>101513</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,32%</t>
         </is>
       </c>
     </row>
@@ -4838,12 +4838,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11566</t>
+          <t>10346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23986</t>
+          <t>24198</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16023</t>
+          <t>16502</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31141</t>
+          <t>31413</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>30514</t>
+          <t>30749</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>50900</t>
+          <t>50490</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>439118</t>
+          <t>437997</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>478984</t>
+          <t>479318</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>472449</t>
+          <t>470904</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>515004</t>
+          <t>513778</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>924459</t>
+          <t>924272</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>983019</t>
+          <t>981435</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>67,86%</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>160046</t>
+          <t>158543</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>196175</t>
+          <t>197663</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>154001</t>
+          <t>156565</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>192618</t>
+          <t>193426</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>325908</t>
+          <t>324861</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>379028</t>
+          <t>378203</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,15%</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>53836</t>
+          <t>52900</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>79214</t>
+          <t>77780</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>64530</t>
+          <t>63987</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>92369</t>
+          <t>91419</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>124306</t>
+          <t>124477</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>162039</t>
+          <t>159978</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -5756,12 +5756,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39201</t>
+          <t>38528</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48797</t>
+          <t>48321</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44513</t>
+          <t>44456</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54122</t>
+          <t>54102</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>87236</t>
+          <t>86037</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>100505</t>
+          <t>100154</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,19%</t>
         </is>
       </c>
     </row>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4553</t>
+          <t>4681</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12665</t>
+          <t>13266</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>4080</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12115</t>
+          <t>12469</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10393</t>
+          <t>10413</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21260</t>
+          <t>21914</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,42%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>2396</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10044</t>
+          <t>8995</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1787</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8155</t>
+          <t>8032</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>5487</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14594</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -6212,12 +6212,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>117588</t>
+          <t>117356</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>134235</t>
+          <t>133862</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>119249</t>
+          <t>117761</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>139156</t>
+          <t>139902</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>242427</t>
+          <t>243153</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>268522</t>
+          <t>269945</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>79,29%</t>
         </is>
       </c>
     </row>
@@ -6325,12 +6325,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9897</t>
+          <t>9454</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21592</t>
+          <t>20647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21176</t>
+          <t>20256</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37095</t>
+          <t>35893</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>33804</t>
+          <t>32275</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>53587</t>
+          <t>52306</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11384</t>
+          <t>10727</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23710</t>
+          <t>24251</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17570</t>
+          <t>17429</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34087</t>
+          <t>34457</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32067</t>
+          <t>32277</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53320</t>
+          <t>53246</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -6668,12 +6668,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>115994</t>
+          <t>116124</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>136097</t>
+          <t>135447</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>149425</t>
+          <t>150079</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>173381</t>
+          <t>174099</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>272207</t>
+          <t>274096</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>303875</t>
+          <t>304653</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>79,04%</t>
         </is>
       </c>
     </row>
@@ -6781,12 +6781,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23540</t>
+          <t>22994</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40400</t>
+          <t>41405</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19753</t>
+          <t>19018</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40728</t>
+          <t>40165</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47561</t>
+          <t>46860</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75242</t>
+          <t>75070</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,48%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10141</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23409</t>
+          <t>22677</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12584</t>
+          <t>13864</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29938</t>
+          <t>29840</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27045</t>
+          <t>25858</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48171</t>
+          <t>47227</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,25%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>133157</t>
+          <t>134930</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>216862</t>
+          <t>215587</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>221362</t>
+          <t>220524</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>252389</t>
+          <t>253374</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>365924</t>
+          <t>354701</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>457849</t>
+          <t>459797</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>79,15%</t>
         </is>
       </c>
     </row>
@@ -7237,12 +7237,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41443</t>
+          <t>41774</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>131544</t>
+          <t>128374</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34547</t>
+          <t>34328</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63662</t>
+          <t>64581</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>86130</t>
+          <t>83262</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>187350</t>
+          <t>193153</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>33,25%</t>
         </is>
       </c>
     </row>
@@ -7350,12 +7350,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10189</t>
+          <t>10681</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24514</t>
+          <t>25718</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>12298</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29762</t>
+          <t>28235</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>26246</t>
+          <t>26882</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>49607</t>
+          <t>49596</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7435,7 +7435,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>423296</t>
+          <t>410265</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>517636</t>
+          <t>517139</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>558493</t>
+          <t>558039</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>605025</t>
+          <t>605183</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1005769</t>
+          <t>999638</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1107058</t>
+          <t>1106032</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,57%</t>
         </is>
       </c>
     </row>
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>94219</t>
+          <t>91954</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>194047</t>
+          <t>204289</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>92074</t>
+          <t>91371</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>130986</t>
+          <t>130487</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7743,12 +7743,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>195725</t>
+          <t>198797</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>303754</t>
+          <t>307113</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,54%</t>
         </is>
       </c>
     </row>
@@ -7806,12 +7806,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42850</t>
+          <t>43018</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>66454</t>
+          <t>66814</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>56054</t>
+          <t>54324</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>85387</t>
+          <t>85544</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>105277</t>
+          <t>106374</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>143872</t>
+          <t>143721</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,08%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP05A07-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP05A07-Edad-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>83793</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>73811</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>93424</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>57,4%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>50,56%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>63,99%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>78415</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>68627</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>88116</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>68931</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>88262</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>53,66%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>46,96%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>60,3%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>83793</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>73756</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>93330</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>57,4%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>147567</t>
+          <t>148825</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>175532</t>
+          <t>176190</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,31%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>42133</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>33448</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>51256</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>28,86%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>22,91%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>35,11%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>50238</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>41808</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>60482</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>41536</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>58898</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>34,38%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>28,61%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>41,39%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>42133</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>33142</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>51458</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>28,86%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>79524</t>
+          <t>80083</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>106063</t>
+          <t>106704</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,53%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20064</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>13788</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>27554</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>13,74%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>9,44%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>18,87%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>17481</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>11828</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>24478</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>11072</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>24349</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>11,96%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,09%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>16,75%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>20064</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>14359</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>27698</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>13,74%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28286</t>
+          <t>28338</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>47909</t>
+          <t>47553</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,28%</t>
         </is>
       </c>
     </row>
@@ -1061,57 +1061,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>145990</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>145990</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>145990</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>146134</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>146134</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>146134</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>145990</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>145990</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>145990</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>134974</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>120979</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>148137</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>50,18%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>44,98%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>55,07%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>126346</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>113889</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>138922</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>113363</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>138877</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>53,48%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>48,21%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>58,8%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>134974</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>121704</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>147692</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>50,18%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>241639</t>
+          <t>242171</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>278384</t>
+          <t>279528</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>55,33%</t>
         </is>
       </c>
     </row>
@@ -1291,72 +1291,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>97800</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>85887</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>112093</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>36,36%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>31,93%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>41,67%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>88403</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>75928</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>100362</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>75936</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>101156</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>37,42%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>32,14%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>42,48%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>97800</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>85087</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>111142</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>36,36%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>31,63%</t>
-        </is>
-      </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>168469</t>
+          <t>168534</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>205788</t>
+          <t>205558</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,69%</t>
         </is>
       </c>
     </row>
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>36217</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>27377</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>46296</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13,46%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>10,18%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>17,21%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>21501</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>15438</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>30052</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>14141</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>29701</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>9,1%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,53%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,72%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>36217</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>27598</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>46004</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>13,46%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47081</t>
+          <t>47021</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71506</t>
+          <t>71131</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -1517,57 +1517,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>236250</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1634,72 +1634,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>78160</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>68290</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>89334</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>49,29%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>43,07%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>56,34%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>88341</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>79138</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>99457</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>77769</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>99439</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>56,25%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>50,39%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>63,33%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>78160</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>68103</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>89108</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>49,29%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>150031</t>
+          <t>152150</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>181941</t>
+          <t>181936</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,64%</t>
         </is>
       </c>
     </row>
@@ -1747,72 +1747,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>59826</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>50182</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>70268</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>37,73%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>31,65%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>44,31%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>47766</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>38141</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>57126</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>37837</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>57422</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>30,42%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>24,29%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>36,38%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>59826</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>49393</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>69900</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>37,73%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>93320</t>
+          <t>94109</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>123502</t>
+          <t>122338</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>38,76%</t>
         </is>
       </c>
     </row>
@@ -1865,67 +1865,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>20585</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>13841</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>28342</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>12,98%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>8,73%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>17,87%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>20936</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>14547</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>28277</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>14747</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>29517</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>13,33%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>9,26%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>18,01%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>20585</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>14946</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>28718</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>12,98%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31311</t>
+          <t>32581</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51827</t>
+          <t>53023</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,8%</t>
         </is>
       </c>
     </row>
@@ -1973,57 +1973,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>157043</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2090,72 +2090,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>99701</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>87905</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>110357</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>55,4%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>48,85%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>61,32%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>87948</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>77831</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>99280</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>77457</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>99271</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>51,56%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>45,63%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>58,21%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>99701</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>88701</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>110296</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>55,4%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>172373</t>
+          <t>172180</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>201355</t>
+          <t>201579</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,51%</t>
         </is>
       </c>
     </row>
@@ -2203,72 +2203,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>61192</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>50697</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>72891</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>34,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>28,17%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>40,51%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>56250</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>47078</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>66776</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>45608</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>66592</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>32,98%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>27,6%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>39,15%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>61192</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>51666</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>72198</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>34,0%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>102367</t>
+          <t>102774</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>131649</t>
+          <t>131273</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,45%</t>
         </is>
       </c>
     </row>
@@ -2316,72 +2316,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>19062</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>13291</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>26438</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>10,59%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>7,39%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>14,69%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>26372</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>18622</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34642</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>20038</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>35032</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>15,46%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>10,92%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>20,31%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>19062</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>13109</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>25885</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>10,59%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>36217</t>
+          <t>35553</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>56208</t>
+          <t>57382</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -2429,57 +2429,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>170569</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>170569</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>170569</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2546,72 +2546,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>396627</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>372837</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>417410</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>52,64%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>49,48%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>55,4%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>553</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>381050</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>359659</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>402182</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>360552</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>404369</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>53,67%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>50,66%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>56,65%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>571</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>396627</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>373723</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>418506</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>52,64%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>745526</t>
+          <t>747006</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>809093</t>
+          <t>807229</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,16%</t>
         </is>
       </c>
     </row>
@@ -2659,72 +2659,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>260952</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>239795</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>282585</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>34,63%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>31,82%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>37,5%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>348</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>242657</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>223314</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>263770</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>219620</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>262769</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>34,18%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>31,45%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>37,15%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>367</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>260952</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>242236</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>286961</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>34,63%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>472162</t>
+          <t>476942</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>533286</t>
+          <t>534677</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,53%</t>
         </is>
       </c>
     </row>
@@ -2772,72 +2772,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>95928</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>81296</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>111853</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>12,73%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>10,79%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>14,84%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>86289</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>73045</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>102445</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>73036</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>100948</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>12,15%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>10,29%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>14,43%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>95928</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>80006</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>111102</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>12,73%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>10,62%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>163777</t>
+          <t>161806</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>204858</t>
+          <t>203673</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -2885,57 +2885,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1074</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>753507</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>753507</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>753507</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1023</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>709996</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>709996</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>709996</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1074</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>753507</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>753507</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>753507</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3055,7 +3055,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3066,7 +3066,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>88957</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>81044</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>96276</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>71,64%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>65,27%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>77,54%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>143</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>88538</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>80313</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>96918</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>80589</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>96840</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>67,53%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>61,26%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>73,92%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>88957</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>80277</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>96685</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>71,64%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>165465</t>
+          <t>166381</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>188440</t>
+          <t>189022</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>74,05%</t>
         </is>
       </c>
     </row>
@@ -3347,72 +3347,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>26984</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>20741</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>35630</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>21,73%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>28,7%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>30687</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>23027</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>38187</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>23251</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>38179</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>23,41%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>17,56%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>29,13%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>26984</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>20267</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>35136</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>21,73%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47951</t>
+          <t>47100</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69179</t>
+          <t>68684</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,91%</t>
         </is>
       </c>
     </row>
@@ -3460,72 +3460,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8224</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4417</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>13497</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6,62%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>10,87%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>11886</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>7372</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>17417</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>7502</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>18291</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>9,07%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,62%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>13,28%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>8224</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>3973</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>12983</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>6,62%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14326</t>
+          <t>14598</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28905</t>
+          <t>28154</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -3573,57 +3573,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>131111</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>131111</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>131111</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3690,72 +3690,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>171430</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>157917</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>183938</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>66,43%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>61,19%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>71,28%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>137506</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>126903</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>148248</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>126575</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>148314</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>65,5%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>60,45%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>70,61%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>171430</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>158352</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>183195</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>66,43%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>292082</t>
+          <t>292186</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>325284</t>
+          <t>325322</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,51%</t>
         </is>
       </c>
     </row>
@@ -3803,72 +3803,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>61841</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>50669</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>73414</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>23,96%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>19,63%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>28,45%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>55843</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>45860</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>65965</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>46330</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>65851</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>26,6%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>21,84%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>31,42%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>61841</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>51945</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>73864</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>23,96%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>103783</t>
+          <t>103079</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>134257</t>
+          <t>133647</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,56%</t>
         </is>
       </c>
     </row>
@@ -3916,72 +3916,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>24790</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>17882</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>33097</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,61%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,93%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12,83%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>16597</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>10691</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>23357</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>10497</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>22820</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>7,91%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,09%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,13%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>24790</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>17435</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>33194</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,61%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32202</t>
+          <t>32275</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52046</t>
+          <t>52184</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -4029,57 +4029,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>331</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>209946</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>209946</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>209946</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4146,72 +4146,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>122797</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>112461</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>133682</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>65,35%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>59,85%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>71,15%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>179</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>124295</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>113887</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>135120</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>113454</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>134499</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>65,8%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>60,29%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>71,53%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>122797</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>111407</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>133211</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>65,35%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>231891</t>
+          <t>230747</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>263037</t>
+          <t>260801</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>69,22%</t>
         </is>
       </c>
     </row>
@@ -4259,72 +4259,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>43885</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>34544</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>53666</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>23,36%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>18,38%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>28,56%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>45003</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>35533</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>55242</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>35895</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>54882</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>23,82%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>18,81%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>29,24%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>43885</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>33641</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>54009</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>23,36%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>76392</t>
+          <t>76182</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103218</t>
+          <t>103380</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,44%</t>
         </is>
       </c>
     </row>
@@ -4372,72 +4372,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>21212</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14917</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>29732</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>11,29%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>7,94%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>15,82%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>19601</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>13169</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>27117</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>13662</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>27611</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>10,38%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>6,97%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>14,36%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>21212</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>14425</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>29035</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>11,29%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31573</t>
+          <t>32077</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51268</t>
+          <t>52264</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -4485,57 +4485,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>187894</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>187894</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>187894</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>187894</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>187894</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>187894</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4602,72 +4602,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>110304</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>99394</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>120803</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>63,38%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>57,11%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>69,41%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>108801</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>97765</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>119502</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>98764</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>120352</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>63,21%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>56,8%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>69,42%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>110304</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>100394</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>120846</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>63,38%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>204060</t>
+          <t>203951</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>231666</t>
+          <t>234474</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>67,73%</t>
         </is>
       </c>
     </row>
@@ -4715,72 +4715,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>40731</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>31531</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>51353</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>23,4%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>18,12%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>29,5%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>46446</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>36650</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>57520</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>36132</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>56676</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>26,98%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>21,29%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>33,42%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>40731</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>32260</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>51009</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>23,4%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>74966</t>
+          <t>74558</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>101513</t>
+          <t>101551</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,33%</t>
         </is>
       </c>
     </row>
@@ -4828,72 +4828,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>23013</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>16347</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>31507</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>13,22%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>9,39%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>18,1%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>16886</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>10346</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>24198</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>11097</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>24297</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>9,81%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>6,01%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>14,06%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>23013</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>16502</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>31413</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>13,22%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>30749</t>
+          <t>31216</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>50490</t>
+          <t>50204</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -4941,57 +4941,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>172133</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>172133</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>172133</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5058,72 +5058,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>493486</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>471451</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>514241</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>66,31%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>63,35%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>69,1%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>693</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>459140</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>437997</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>479318</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>439424</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>479630</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>65,4%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>62,38%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>68,27%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>701</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>493486</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>470904</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>513778</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>66,31%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>924272</t>
+          <t>922504</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>981435</t>
+          <t>982155</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>67,91%</t>
         </is>
       </c>
     </row>
@@ -5171,72 +5171,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>173441</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>156287</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>193765</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>23,31%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>21,0%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>26,04%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>268</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>177979</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>158543</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>197663</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>160443</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>197385</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>25,35%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>22,58%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>28,15%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>173441</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>156565</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>193426</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>23,31%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>324861</t>
+          <t>324986</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>378203</t>
+          <t>377358</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,09%</t>
         </is>
       </c>
     </row>
@@ -5284,72 +5284,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>77239</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>63623</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>90263</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>10,38%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>8,55%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>12,13%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>64969</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>52900</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>77780</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>53358</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>77694</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>9,25%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>7,53%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>11,08%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>77239</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>63987</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>91419</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>10,38%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>124477</t>
+          <t>124675</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>159978</t>
+          <t>162827</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -5397,57 +5397,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1064</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>744166</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>744166</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>744166</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1058</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>702089</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>702089</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>702089</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1064</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>744166</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>744166</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>744166</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5578,7 +5578,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5746,72 +5746,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>40546</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>36270</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>44045</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>80,23%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>71,77%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>87,15%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>44186</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>38528</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>48321</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>76,83%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>66,99%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>84,02%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>49974</t>
+          <t>39391</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44456</t>
+          <t>33876</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54102</t>
+          <t>43493</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5821,32 +5821,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>94160</t>
+          <t>79937</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>86037</t>
+          <t>73738</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>100154</t>
+          <t>85529</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>83,34%</t>
         </is>
       </c>
     </row>
@@ -5859,72 +5859,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6135</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3578</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10124</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>12,14%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>7,08%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>20,03%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>8174</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4681</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>13266</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>14,21%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8,14%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>23,07%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7346</t>
+          <t>7360</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4080</t>
+          <t>4342</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12469</t>
+          <t>11520</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5934,32 +5934,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>15520</t>
+          <t>13495</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10413</t>
+          <t>9016</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21914</t>
+          <t>18567</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -5972,107 +5972,107 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3856</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1724</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7994</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7,63%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>15,82%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5151</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2396</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8995</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>5338</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2711</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>10,25%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>5,2%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>19,77%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>9194</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>5285</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>14675</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>8,96%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>15,64%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>4124</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1787</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>8032</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>6,71%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>2,91%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>13,07%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>9274</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>5487</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>14611</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>7,8%</t>
-        </is>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -6085,57 +6085,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6202,72 +6202,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>110756</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>100894</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>119428</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>70,31%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>64,05%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>75,82%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>205</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>126500</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>117356</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>133862</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>80,12%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>74,33%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>84,79%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>129718</t>
+          <t>114586</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>117761</t>
+          <t>106357</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>139902</t>
+          <t>120904</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6277,32 +6277,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>256218</t>
+          <t>225341</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>243153</t>
+          <t>212393</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>269945</t>
+          <t>236303</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>78,11%</t>
         </is>
       </c>
     </row>
@@ -6315,72 +6315,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>24940</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>18681</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>33470</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>15,83%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>11,86%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>21,25%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>14494</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>9454</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>20647</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>9,18%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>5,99%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>13,08%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27938</t>
+          <t>14368</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20256</t>
+          <t>9632</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35893</t>
+          <t>20502</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6390,32 +6390,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>42433</t>
+          <t>39308</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>32275</t>
+          <t>31517</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>52306</t>
+          <t>49775</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -6428,72 +6428,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>21826</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>15249</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>29338</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13,86%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>9,68%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>18,62%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>16888</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>10727</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>24251</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,7%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,79%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15,36%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>24898</t>
+          <t>16068</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17429</t>
+          <t>11028</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34457</t>
+          <t>23429</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6503,32 +6503,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>41786</t>
+          <t>37893</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32277</t>
+          <t>29017</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53246</t>
+          <t>47297</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -6541,57 +6541,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>157882</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>157882</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>157882</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145021</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145021</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145021</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6616,17 +6616,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>340437</t>
+          <t>302542</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>340437</t>
+          <t>302542</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>340437</t>
+          <t>302542</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6658,72 +6658,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>155852</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>144944</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166236</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>78,25%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>72,77%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>83,46%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>126709</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>116124</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>135447</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>72,87%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>66,78%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>77,89%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>163475</t>
+          <t>126073</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>150079</t>
+          <t>115053</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>174099</t>
+          <t>135971</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6733,32 +6733,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>290183</t>
+          <t>281924</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>274096</t>
+          <t>266344</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>304653</t>
+          <t>296905</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>79,24%</t>
         </is>
       </c>
     </row>
@@ -6771,72 +6771,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>24472</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>16775</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>33697</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12,29%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8,42%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>16,92%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>31601</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>22994</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>41405</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>18,17%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>13,22%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>23,81%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27491</t>
+          <t>33463</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19018</t>
+          <t>25275</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40165</t>
+          <t>43555</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6846,32 +6846,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>59092</t>
+          <t>57935</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46860</t>
+          <t>46400</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75070</t>
+          <t>71856</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,18%</t>
         </is>
       </c>
     </row>
@@ -6884,72 +6884,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>18845</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>12215</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>27625</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>9,46%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>6,13%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>13,87%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>15577</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>9856</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>22677</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>8,96%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>5,67%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>13,04%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>20581</t>
+          <t>15983</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13864</t>
+          <t>10769</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29840</t>
+          <t>23662</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6959,32 +6959,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>36159</t>
+          <t>34828</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25858</t>
+          <t>25538</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47227</t>
+          <t>45951</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -6997,57 +6997,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>199169</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>199169</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>199169</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>211547</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>211547</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>211547</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7072,17 +7072,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>385434</t>
+          <t>374686</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>385434</t>
+          <t>374686</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>385434</t>
+          <t>374686</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7114,72 +7114,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>225569</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>207901</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>238834</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>77,08%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>71,04%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>81,61%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>191370</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>134930</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>215587</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>69,47%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>48,98%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>78,26%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>238571</t>
+          <t>194199</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>220524</t>
+          <t>180925</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>253374</t>
+          <t>206195</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>429941</t>
+          <t>419768</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>354701</t>
+          <t>398041</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>459797</t>
+          <t>439366</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>80,0%</t>
         </is>
       </c>
     </row>
@@ -7227,72 +7227,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>47328</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>35851</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>64537</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>16,17%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>12,25%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>22,05%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>67344</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>41774</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>128374</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>24,45%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>15,17%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>46,6%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>46907</t>
+          <t>44476</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34328</t>
+          <t>34674</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>64581</t>
+          <t>57262</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7302,32 +7302,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>114250</t>
+          <t>91804</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>83262</t>
+          <t>75643</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>193153</t>
+          <t>110202</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -7340,72 +7340,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>19747</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>13062</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>30859</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>6,75%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4,46%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>10,54%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>16744</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>10681</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>25718</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>6,08%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>3,88%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>9,34%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>20005</t>
+          <t>17878</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12298</t>
+          <t>11836</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28235</t>
+          <t>27275</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7415,32 +7415,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>36749</t>
+          <t>37626</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>26882</t>
+          <t>27911</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>49596</t>
+          <t>48957</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -7458,17 +7458,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7493,17 +7493,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7528,17 +7528,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7570,72 +7570,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>532723</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>511552</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>554024</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>76,12%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>73,09%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>79,16%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>722</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>488765</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>410265</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>517139</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>73,53%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>61,72%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>77,8%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>748</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>581738</t>
+          <t>474248</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>558039</t>
+          <t>454972</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>605183</t>
+          <t>492195</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1070503</t>
+          <t>1006971</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>999638</t>
+          <t>976782</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1106032</t>
+          <t>1034906</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,87%</t>
         </is>
       </c>
     </row>
@@ -7683,72 +7683,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>102875</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>85200</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>121560</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>14,7%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>12,17%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>17,37%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>121613</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>91954</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>204289</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>18,29%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>13,83%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>30,73%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>109682</t>
+          <t>99667</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>91371</t>
+          <t>85042</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>130487</t>
+          <t>117071</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7758,32 +7758,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>231295</t>
+          <t>202542</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>198797</t>
+          <t>177443</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>307113</t>
+          <t>227125</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>17,09%</t>
         </is>
       </c>
     </row>
@@ -7796,72 +7796,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>64274</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>51615</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>79534</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>9,18%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>7,37%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>11,36%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>54360</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>43018</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>66814</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>8,18%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>6,47%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>10,05%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>69608</t>
+          <t>55267</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>54324</t>
+          <t>43313</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>85544</t>
+          <t>67242</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7871,32 +7871,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>123969</t>
+          <t>119541</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>106374</t>
+          <t>103289</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>143721</t>
+          <t>141051</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -7909,57 +7909,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7984,17 +7984,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1425767</t>
+          <t>1329054</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1425767</t>
+          <t>1329054</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1425767</t>
+          <t>1329054</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
